--- a/data/trans_dic/P1408-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P1408-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 4,05</t>
+          <t>0,85; 4,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,69</t>
+          <t>0,0; 1,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,43</t>
+          <t>0,6; 3,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,18</t>
+          <t>0,58; 2,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,46</t>
+          <t>0,58; 3,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,29</t>
+          <t>0,0; 1,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,07</t>
+          <t>0,0; 1,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,29</t>
+          <t>0,55; 2,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,99</t>
+          <t>1,04; 3,24</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,05</t>
+          <t>0,12; 1,07</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,04</t>
+          <t>0,48; 2,05</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 1,81</t>
+          <t>0,69; 1,77</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,49; 6,53</t>
+          <t>2,44; 6,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 4,03</t>
+          <t>0,26; 3,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,37</t>
+          <t>0,0; 1,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,44</t>
+          <t>0,53; 2,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,82</t>
+          <t>0,7; 3,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,48</t>
+          <t>0,0; 1,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,24</t>
+          <t>0,26; 2,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,73</t>
+          <t>0,82; 2,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,39</t>
+          <t>1,87; 4,4</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,17</t>
+          <t>0,27; 2,26</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,51</t>
+          <t>0,14; 1,38</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,1</t>
+          <t>0,81; 2,02</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -997,32 +997,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,15; 6,91</t>
+          <t>2,94; 6,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,46; 4,57</t>
+          <t>1,58; 4,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,84</t>
+          <t>1,06; 3,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 4,03</t>
+          <t>1,96; 5,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 7,78</t>
+          <t>1,28; 7,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,32</t>
+          <t>0,37; 3,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,27 +1032,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,32; 7,03</t>
+          <t>2,27; 7,3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,19; 6,42</t>
+          <t>2,96; 6,08</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,45; 3,65</t>
+          <t>1,41; 3,56</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,88</t>
+          <t>0,84; 2,81</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,03; 4,09</t>
+          <t>2,4; 5,22</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,39; 5,76</t>
+          <t>3,46; 5,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,35; 4,49</t>
+          <t>2,28; 4,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,61</t>
+          <t>1,71; 3,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,43; 4,41</t>
+          <t>2,22; 4,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,03; 4,57</t>
+          <t>2,08; 4,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,36</t>
+          <t>0,14; 1,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,34</t>
+          <t>0,61; 2,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,22</t>
+          <t>1,12; 2,62</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,17; 5,16</t>
+          <t>3,29; 4,93</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,55; 2,91</t>
+          <t>1,55; 3,01</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,43; 2,75</t>
+          <t>1,45; 2,82</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,09</t>
+          <t>1,99; 3,31</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,71; 10,36</t>
+          <t>4,81; 10,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,14</t>
+          <t>1,19; 3,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,47; 3,96</t>
+          <t>1,37; 4,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,09; 6,69</t>
+          <t>2,8; 5,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,52; 4,16</t>
+          <t>1,44; 4,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,86</t>
+          <t>1,46; 3,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,1</t>
+          <t>0,95; 3,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,54; 5,2</t>
+          <t>3,04; 5,86</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,17; 5,84</t>
+          <t>3,23; 5,79</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,36</t>
+          <t>1,55; 3,34</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,47; 3,04</t>
+          <t>1,38; 2,92</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,94; 5,09</t>
+          <t>3,27; 5,21</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,96</t>
+          <t>0,3; 3,06</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1427,52 +1427,52 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,01</t>
+          <t>0,31; 2,85</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,63</t>
+          <t>0,0; 1,37</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,1; 3,99</t>
+          <t>2,09; 4,09</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,24</t>
+          <t>0,75; 2,24</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,23</t>
+          <t>0,71; 2,21</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,7; 3,34</t>
+          <t>1,66; 3,33</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,85; 3,53</t>
+          <t>1,93; 3,61</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,81</t>
+          <t>0,62; 1,78</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,75; 1,95</t>
+          <t>0,74; 1,99</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,43; 2,75</t>
+          <t>1,39; 2,66</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,44; 4,87</t>
+          <t>3,49; 4,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,63; 2,67</t>
+          <t>1,65; 2,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,48; 2,43</t>
+          <t>1,53; 2,49</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,81; 2,9</t>
+          <t>2,08; 3,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,19; 3,35</t>
+          <t>2,22; 3,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,86; 1,64</t>
+          <t>0,87; 1,69</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,9; 1,68</t>
+          <t>0,86; 1,68</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,85; 2,84</t>
+          <t>2,02; 2,88</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,01; 3,88</t>
+          <t>3,03; 3,91</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,39; 2,0</t>
+          <t>1,39; 2,05</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,31; 1,91</t>
+          <t>1,31; 1,9</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,98; 2,72</t>
+          <t>2,18; 2,85</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5446</t>
+          <t>6551</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5476</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10763</t>
+          <t>12027</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4770; 19175</t>
+          <t>4039; 19170</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 7397</t>
+          <t>0; 6128</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2658; 14735</t>
+          <t>2592; 13871</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2529; 11020</t>
+          <t>3188; 13376</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1759; 10611</t>
+          <t>1765; 10221</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4068</t>
+          <t>0; 5280</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 7175</t>
+          <t>0; 6511</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2489; 10230</t>
+          <t>2671; 10220</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7652; 23300</t>
+          <t>8116; 25285</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>930; 7890</t>
+          <t>933; 8048</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3840; 15844</t>
+          <t>3752; 15900</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6355; 17273</t>
+          <t>7214; 18433</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5541</t>
+          <t>5760</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6003</t>
+          <t>6315</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11544</t>
+          <t>12076</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9135; 23972</t>
+          <t>8958; 23871</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1079; 16877</t>
+          <t>1075; 16422</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5151</t>
+          <t>0; 5809</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2429; 11049</t>
+          <t>2561; 11557</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2554; 14210</t>
+          <t>2594; 14589</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4986</t>
+          <t>0; 4147</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>973; 8332</t>
+          <t>982; 9310</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3004; 10440</t>
+          <t>3456; 11742</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14294; 32446</t>
+          <t>13810; 32504</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1966; 16451</t>
+          <t>2019; 17101</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1046; 11330</t>
+          <t>1034; 10340</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6962; 17525</t>
+          <t>7300; 18323</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14304</t>
+          <t>14763</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7187</t>
+          <t>7948</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21491</t>
+          <t>22712</t>
         </is>
       </c>
     </row>
@@ -2343,32 +2343,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>17084; 37485</t>
+          <t>15942; 35904</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9198; 28751</t>
+          <t>9936; 28034</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5965; 20039</t>
+          <t>5556; 18708</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4263; 26831</t>
+          <t>9208; 23692</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2290; 13048</t>
+          <t>2148; 13365</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>966; 8633</t>
+          <t>955; 8498</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2378,27 +2378,27 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3875; 11735</t>
+          <t>4260; 13680</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>22666; 45590</t>
+          <t>20998; 43201</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12889; 32478</t>
+          <t>12569; 31643</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6087; 19829</t>
+          <t>5774; 19323</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8547; 34112</t>
+          <t>15767; 34281</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>33435</t>
+          <t>35477</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>13939</t>
+          <t>14983</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>47374</t>
+          <t>50461</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>42002; 71375</t>
+          <t>42863; 71457</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>27179; 52016</t>
+          <t>26453; 51967</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19993; 41517</t>
+          <t>19657; 41821</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>25155; 45603</t>
+          <t>25083; 46140</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>14484; 32662</t>
+          <t>14840; 33190</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1027; 10375</t>
+          <t>1102; 10502</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5041; 19301</t>
+          <t>5051; 18691</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5716; 21691</t>
+          <t>9615; 22556</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>61976; 100740</t>
+          <t>64307; 96319</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>29909; 56035</t>
+          <t>29899; 57990</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>28306; 54390</t>
+          <t>28571; 55723</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>32065; 62235</t>
+          <t>39733; 65933</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21333</t>
+          <t>23634</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>30033</t>
+          <t>33708</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>51366</t>
+          <t>57343</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>16524; 36300</t>
+          <t>16870; 36126</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6158; 21139</t>
+          <t>6067; 19696</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9133; 24605</t>
+          <t>8506; 25177</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14665; 31712</t>
+          <t>15872; 33240</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>8668; 23662</t>
+          <t>8189; 23292</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10983; 29313</t>
+          <t>11069; 28746</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7159; 22863</t>
+          <t>6984; 22722</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>21217; 43532</t>
+          <t>25113; 48471</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>29123; 53698</t>
+          <t>29732; 53207</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20777; 42737</t>
+          <t>19761; 42507</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>20030; 41309</t>
+          <t>18773; 39616</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>38578; 66700</t>
+          <t>45598; 72670</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>18930</t>
+          <t>20114</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>19941</t>
+          <t>21139</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1066; 8814</t>
+          <t>898; 9127</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2977,52 +2977,52 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>892; 8655</t>
+          <t>891; 8188</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 3922</t>
+          <t>0; 3241</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>26224; 49880</t>
+          <t>26142; 51029</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8370; 24859</t>
+          <t>8350; 24877</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8210; 24161</t>
+          <t>7715; 23896</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>12928; 25370</t>
+          <t>14020; 28081</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>28580; 54643</t>
+          <t>29861; 55799</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8441; 24899</t>
+          <t>8475; 24476</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10279; 26752</t>
+          <t>10081; 27239</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14316; 27489</t>
+          <t>15046; 28745</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>81071</t>
+          <t>87212</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>81410</t>
+          <t>88546</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>162480</t>
+          <t>175757</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>112616; 159237</t>
+          <t>114148; 157257</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>55681; 91374</t>
+          <t>56358; 94232</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>50051; 82291</t>
+          <t>51943; 84151</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>61026; 97798</t>
+          <t>71588; 104365</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>74148; 113033</t>
+          <t>74990; 111704</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>30479; 58068</t>
+          <t>30853; 59798</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31792; 59239</t>
+          <t>30457; 59455</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>66128; 101287</t>
+          <t>73385; 104580</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>200249; 258041</t>
+          <t>201398; 259707</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>96813; 139191</t>
+          <t>96791; 143053</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>90404; 131800</t>
+          <t>90848; 131705</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>137151; 188634</t>
+          <t>154306; 201495</t>
         </is>
       </c>
     </row>
